--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488038_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488038_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1818</v>
+        <v>5.025</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9135</v>
+        <v>3.4479</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2682</v>
+        <v>1.5771</v>
       </c>
       <c r="G2" t="n">
         <v>4.1197</v>
@@ -610,13 +610,13 @@
         <v>2.9733</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8044</v>
+        <v>-0.3524</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9715</v>
+        <v>0.5059</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1672</v>
+        <v>-0.8583</v>
       </c>
       <c r="V2" t="n">
         <v>0.2666</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. DOMINGOS</t>
+          <t>J. MORALES MUÑOZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9079</v>
+        <v>0.9053</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0633</v>
+        <v>0.9053</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8446</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8686</v>
+        <v>0.9053</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1535</v>
+        <v>0.3027</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2849</v>
+        <v>0.6027</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.3695</v>
+        <v>0.9053</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4901</v>
+        <v>0.3027</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1205</v>
+        <v>0.6027</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4991</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6634</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1643</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.3876</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5274</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5955</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.06809999999999999</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6366</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8107</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.174</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MORALES MUÑOZ</t>
+          <t>K. DOMINGOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9053</v>
+        <v>0.3018</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9053</v>
+        <v>-0.4023</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.7042</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9053</v>
+        <v>-0.8686</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3027</v>
+        <v>-1.1535</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6027</v>
+        <v>0.2849</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9053</v>
+        <v>-0.3695</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3027</v>
+        <v>-0.4901</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6027</v>
+        <v>0.1205</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-0.4991</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.6634</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.1643</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.5858</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>0.9214</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.1299</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0.2085</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.6366</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.8107</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.174</v>
       </c>
     </row>
     <row r="5">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2244</v>
+        <v>0.1401</v>
       </c>
       <c r="E6" t="n">
         <v>0.0398</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1845</v>
+        <v>0.1003</v>
       </c>
       <c r="G6" t="n">
         <v>0.365</v>
@@ -922,13 +922,13 @@
         <v>0.3964</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5371</v>
+        <v>-0.6213</v>
       </c>
       <c r="T6" t="n">
         <v>-0.2496</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2875</v>
+        <v>-0.3717</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ESPINAL REYNOSO</t>
+          <t>F. DAYER</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4105</v>
+        <v>-0.2412</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9007</v>
+        <v>0.428</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4903</v>
+        <v>-0.6692</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7752</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1378</v>
+        <v>-1.8588</v>
       </c>
       <c r="I7" t="n">
-        <v>1.913</v>
+        <v>2.8583</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1855</v>
+        <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0611</v>
+        <v>-0.3223</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1244</v>
+        <v>2.4223</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5897</v>
+        <v>-1.1005</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1989</v>
+        <v>-1.5365</v>
       </c>
       <c r="O7" t="n">
-        <v>1.7885</v>
+        <v>0.436</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7929</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7751</v>
+        <v>1.784</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5049</v>
+        <v>-0.4809</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3706</v>
+        <v>-0.1724</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1343</v>
+        <v>-0.3085</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4737</v>
+        <v>0.4295</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2666</v>
+        <v>1.4737</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7403</v>
+        <v>-1.0442</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. DAYER</t>
+          <t>J. ESPINAL REYNOSO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8939</v>
+        <v>-0.4637</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4493</v>
+        <v>-1.5327</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4446</v>
+        <v>1.0691</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.7752</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8588</v>
+        <v>-1.1378</v>
       </c>
       <c r="I8" t="n">
-        <v>2.8583</v>
+        <v>1.913</v>
       </c>
       <c r="J8" t="n">
-        <v>2.1</v>
+        <v>0.1855</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3223</v>
+        <v>0.0611</v>
       </c>
       <c r="L8" t="n">
-        <v>2.4223</v>
+        <v>0.1244</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1005</v>
+        <v>0.5897</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5365</v>
+        <v>-1.1989</v>
       </c>
       <c r="O8" t="n">
-        <v>0.436</v>
+        <v>1.7885</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R8" t="n">
-        <v>1.784</v>
+        <v>2.7751</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1336</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0497</v>
+        <v>-0.0026</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0839</v>
+        <v>-0.5555</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4295</v>
+        <v>-1.4737</v>
       </c>
       <c r="W8" t="n">
-        <v>1.4737</v>
+        <v>0.2666</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0442</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9905</v>
+        <v>-0.7587</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7415</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.249</v>
+        <v>-0.2209</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8110000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1795</v>
+        <v>0.0523</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0624</v>
+        <v>0.1413</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1171</v>
+        <v>-0.089</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6779</v>
+        <v>-2.2194</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6748</v>
+        <v>-2.2444</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0031</v>
+        <v>0.025</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3282</v>
@@ -1234,13 +1234,13 @@
         <v>2.3787</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8476</v>
+        <v>-0.3891</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.253</v>
+        <v>0.1774</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5946</v>
+        <v>-0.5665</v>
       </c>
       <c r="V10" t="n">
         <v>0.0925</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0639</v>
+        <v>-3.6959</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8377</v>
+        <v>-3.4697</v>
       </c>
       <c r="F11" t="n">
         <v>-0.2262</v>
@@ -1312,10 +1312,10 @@
         <v>1.3876</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0624</v>
+        <v>0.4304</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3892</v>
+        <v>0.7572</v>
       </c>
       <c r="U11" t="n">
         <v>-0.3268</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.1204</v>
+        <v>-5.3449</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.6094</v>
+        <v>-5.8339</v>
       </c>
       <c r="F12" t="n">
         <v>0.489</v>
@@ -1390,10 +1390,10 @@
         <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0756</v>
+        <v>-0.3001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6129</v>
+        <v>0.1625</v>
       </c>
       <c r="U12" t="n">
         <v>-0.4626</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.8754</v>
+        <v>-6.8377</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.487</v>
+        <v>-7.9547</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6116</v>
+        <v>1.117</v>
       </c>
       <c r="G13" t="n">
         <v>-1.7958</v>
@@ -1468,13 +1468,13 @@
         <v>1.9822</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.2671</v>
+        <v>-0.2294</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5578</v>
+        <v>-0.0255</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7093</v>
+        <v>-0.2039</v>
       </c>
       <c r="V13" t="n">
         <v>-0.848</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-13.545</v>
+        <v>-12.9212</v>
       </c>
       <c r="E14" t="n">
-        <v>-17.7051</v>
+        <v>-17.0811</v>
       </c>
       <c r="F14" t="n">
-        <v>4.16</v>
+        <v>4.1601</v>
       </c>
       <c r="G14" t="n">
         <v>-1.9892</v>
@@ -1516,10 +1516,10 @@
         <v>-10.1673</v>
       </c>
       <c r="I14" t="n">
-        <v>8.178100000000001</v>
+        <v>8.178100000000002</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6522999999999999</v>
+        <v>0.6523000000000008</v>
       </c>
       <c r="K14" t="n">
         <v>-0.5063999999999997</v>
@@ -1534,7 +1534,7 @@
         <v>-9.6609</v>
       </c>
       <c r="O14" t="n">
-        <v>7.019100000000002</v>
+        <v>7.0191</v>
       </c>
       <c r="P14" t="n">
         <v>-7.9291</v>
@@ -1546,13 +1546,13 @@
         <v>16.8488</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.3494</v>
+        <v>-1.7253</v>
       </c>
       <c r="T14" t="n">
-        <v>1.873600000000001</v>
+        <v>2.4975</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.223100000000001</v>
+        <v>-4.223</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2777</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. ZULUAGA</t>
+          <t>R. CUBERO ROJANO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.4527</v>
+        <v>5.6254</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1441</v>
+        <v>1.1106</v>
       </c>
       <c r="F15" t="n">
-        <v>4.3086</v>
+        <v>4.5149</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0961</v>
+        <v>1.6803</v>
       </c>
       <c r="H15" t="n">
-        <v>2.4479</v>
+        <v>2.1127</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3517</v>
+        <v>-0.4324</v>
       </c>
       <c r="J15" t="n">
-        <v>2.3293</v>
+        <v>1.0907</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0247</v>
+        <v>1.6817</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3046</v>
+        <v>-0.591</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2331</v>
+        <v>0.5897</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4232</v>
+        <v>0.431</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6563</v>
+        <v>0.1586</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3964</v>
+        <v>3.9645</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.9645</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.568</v>
+        <v>3.9645</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4595</v>
+        <v>-0.1652</v>
       </c>
       <c r="T15" t="n">
-        <v>1.039</v>
+        <v>-0.2467</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4205</v>
+        <v>0.0814</v>
       </c>
       <c r="V15" t="n">
-        <v>2.2935</v>
+        <v>0.1459</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7403</v>
+        <v>0.2666</v>
       </c>
       <c r="X15" t="n">
-        <v>0.5532</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. RUEDA SANTAELLA</t>
+          <t>C. ZULUAGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.4439</v>
+        <v>5.4083</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2641</v>
+        <v>0.9403</v>
       </c>
       <c r="F16" t="n">
-        <v>3.1798</v>
+        <v>4.468</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3064</v>
+        <v>2.0961</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7874</v>
+        <v>2.4479</v>
       </c>
       <c r="I16" t="n">
-        <v>1.519</v>
+        <v>-0.3517</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5905</v>
+        <v>2.3293</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9036</v>
+        <v>2.0247</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6869</v>
+        <v>0.3046</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7159</v>
+        <v>-0.2331</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1162</v>
+        <v>0.4232</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8321</v>
+        <v>-0.6563</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3964</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9822</v>
+        <v>-3.9645</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3787</v>
+        <v>3.568</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8618</v>
+        <v>1.4151</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6558</v>
+        <v>0.8353</v>
       </c>
       <c r="U16" t="n">
-        <v>0.206</v>
+        <v>0.5798</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1207</v>
+        <v>2.2935</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1207</v>
+        <v>0.5532</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.2087</v>
+        <v>5.1231</v>
       </c>
       <c r="E17" t="n">
-        <v>4.196</v>
+        <v>3.8904</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0126</v>
+        <v>1.2327</v>
       </c>
       <c r="G17" t="n">
         <v>0.8695000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>2.1805</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1428</v>
+        <v>1.0572</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4134</v>
+        <v>1.1078</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2707</v>
+        <v>-0.0506</v>
       </c>
       <c r="V17" t="n">
         <v>1.016</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. CUBERO ROJANO</t>
+          <t>L. RUEDA SANTAELLA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.0971</v>
+        <v>4.2593</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6012</v>
+        <v>1.4491</v>
       </c>
       <c r="F18" t="n">
-        <v>4.4959</v>
+        <v>2.8102</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6803</v>
+        <v>3.3064</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1127</v>
+        <v>1.7874</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4324</v>
+        <v>1.519</v>
       </c>
       <c r="J18" t="n">
-        <v>1.0907</v>
+        <v>2.5905</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6817</v>
+        <v>1.9036</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.591</v>
+        <v>0.6869</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5897</v>
+        <v>0.7159</v>
       </c>
       <c r="N18" t="n">
-        <v>0.431</v>
+        <v>-0.1162</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1586</v>
+        <v>0.8321</v>
       </c>
       <c r="P18" t="n">
-        <v>3.9645</v>
+        <v>0.3964</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R18" t="n">
-        <v>3.9645</v>
+        <v>2.3787</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6935</v>
+        <v>0.6772</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.756</v>
+        <v>0.8408</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0625</v>
+        <v>-0.1636</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1459</v>
+        <v>-0.1207</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>-0.1207</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.3395</v>
+        <v>2.9892</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9172</v>
+        <v>1.4266</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4223</v>
+        <v>1.5627</v>
       </c>
       <c r="G19" t="n">
         <v>3.2193</v>
@@ -1936,13 +1936,13 @@
         <v>2.3787</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5011</v>
+        <v>0.1487</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5064</v>
+        <v>0.0029</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0053</v>
+        <v>0.1457</v>
       </c>
       <c r="V19" t="n">
         <v>1.2071</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2586</v>
+        <v>1.3275</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2792</v>
+        <v>-1.5662</v>
       </c>
       <c r="F20" t="n">
-        <v>2.5378</v>
+        <v>2.8937</v>
       </c>
       <c r="G20" t="n">
         <v>0.1134</v>
@@ -2014,13 +2014,13 @@
         <v>3.3698</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.8968</v>
+        <v>-0.8278</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8736</v>
+        <v>-0.1605</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0232</v>
+        <v>-0.6673</v>
       </c>
       <c r="V20" t="n">
         <v>-1.3278</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1939</v>
+        <v>0.1083</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.177</v>
+        <v>-2.4826</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3709</v>
+        <v>2.5909</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3187</v>
@@ -2092,13 +2092,13 @@
         <v>3.1716</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5481</v>
+        <v>0.4625</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7894</v>
+        <v>0.4838</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2413</v>
+        <v>-0.0213</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2071</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5866</v>
+        <v>-1.4567</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8663</v>
+        <v>-0.7645</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.6922</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6164</v>
@@ -2170,13 +2170,13 @@
         <v>0.1982</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1685</v>
+        <v>-0.0385</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1872</v>
+        <v>-0.0853</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.7776</v>
+        <v>-1.6477</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1872</v>
+        <v>-0.0853</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5904</v>
+        <v>-1.5623</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9372</v>
@@ -2248,13 +2248,13 @@
         <v>0.1982</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1685</v>
+        <v>-0.0385</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1872</v>
+        <v>-0.0853</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0187</v>
+        <v>0.0468</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8701</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. BALLESTER MANQUE</t>
+          <t>W. HASSAN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0434</v>
+        <v>-1.9448</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.736</v>
+        <v>-3.5294</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3074</v>
+        <v>1.5846</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0652</v>
+        <v>-0.7224</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.5315</v>
+        <v>2.281</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5337</v>
+        <v>-3.0035</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6752</v>
+        <v>-0.146</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2.6029</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6752</v>
+        <v>-2.7489</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.39</v>
+        <v>-0.5765</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5315</v>
+        <v>-0.3219</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1415</v>
+        <v>-0.2545</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.5858</v>
+        <v>-1.784</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9822</v>
+        <v>-3.9645</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3964</v>
+        <v>2.1805</v>
       </c>
       <c r="S24" t="n">
-        <v>0.6076</v>
+        <v>0.5617</v>
       </c>
       <c r="T24" t="n">
-        <v>0.9215</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3139</v>
+        <v>-0.0194</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.1311</v>
+        <v>-2.3746</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.7944</v>
+        <v>-2.2019</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3366</v>
+        <v>-0.1727</v>
       </c>
       <c r="G25" t="n">
         <v>-2.6357</v>
@@ -2404,13 +2404,13 @@
         <v>0.7929</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.3184</v>
       </c>
       <c r="T25" t="n">
-        <v>1.0463</v>
+        <v>0.6388</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4843</v>
+        <v>-0.3203</v>
       </c>
       <c r="V25" t="n">
         <v>0.1408</v>
@@ -2425,7 +2425,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>W. HASSAN</t>
+          <t>P. BALLESTER MANQUE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,58 +2437,58 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.9106</v>
+        <v>-2.5143</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.2425</v>
+        <v>-2.3472</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3319</v>
+        <v>-0.167</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.7224</v>
+        <v>-1.0652</v>
       </c>
       <c r="H26" t="n">
-        <v>2.281</v>
+        <v>-0.5315</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.0035</v>
+        <v>-0.5337</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.146</v>
+        <v>-0.6752</v>
       </c>
       <c r="K26" t="n">
-        <v>2.6029</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.7489</v>
+        <v>-0.6752</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.5765</v>
+        <v>-0.39</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.3219</v>
+        <v>-0.5315</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.2545</v>
+        <v>0.1415</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.784</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.9645</v>
+        <v>-1.9822</v>
       </c>
       <c r="R26" t="n">
-        <v>2.1805</v>
+        <v>0.3964</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4041</v>
+        <v>0.1368</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.132</v>
+        <v>0.3103</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2721</v>
+        <v>-0.1735</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,22 +2515,22 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>13.5451</v>
+        <v>14.903</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.159999999999998</v>
+        <v>-4.160100000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>17.7051</v>
+        <v>19.0635</v>
       </c>
       <c r="G27" t="n">
-        <v>1.989399999999999</v>
+        <v>1.9894</v>
       </c>
       <c r="H27" t="n">
         <v>10.1674</v>
       </c>
       <c r="I27" t="n">
-        <v>-8.178100000000001</v>
+        <v>-8.178100000000002</v>
       </c>
       <c r="J27" t="n">
         <v>2.6417</v>
@@ -2545,7 +2545,7 @@
         <v>-0.6522000000000002</v>
       </c>
       <c r="N27" t="n">
-        <v>0.5064000000000002</v>
+        <v>0.5064000000000001</v>
       </c>
       <c r="O27" t="n">
         <v>-1.1587</v>
@@ -2560,13 +2560,13 @@
         <v>24.778</v>
       </c>
       <c r="S27" t="n">
-        <v>2.3493</v>
+        <v>3.7076</v>
       </c>
       <c r="T27" t="n">
-        <v>4.223000000000001</v>
+        <v>4.222999999999999</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.8738</v>
+        <v>-0.5155000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>1.2776</v>
